--- a/技能展厅.xlsx
+++ b/技能展厅.xlsx
@@ -15,10 +15,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'站点配置'!$A$1:$B$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'技能清单'!$A$1:$P$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'技能清单'!$A$1:$Q$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'价值案例'!$A$1:$J$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'使用指南'!$A$1:$D$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'填写说明'!$A$1:$D$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'填写说明'!$A$1:$D$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -618,12 +618,13 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="38" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="38" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="38" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -679,30 +680,35 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>单次省时(分钟)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>每周次数</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>提升价值</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>量化收益</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>标签</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>推荐位</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>排序权重</t>
         </is>
@@ -761,32 +767,33 @@
 根据下面这段会议记录，整理成向上级请示的公文，请示事项是追加专项预算80万元，语言正式，结尾用「妥否，请批示」。</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>从「找模板—改抬头—调格式—核口径」的半日工，变成一次对话拿到可编辑成稿。</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>单次省 3.5 小时</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>公文,通知,请示,红头</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>已上线</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>100</v>
       </c>
     </row>
@@ -843,32 +850,33 @@
 这是1小时的评审会转写稿，帮我提炼5条关键决议和3个待办，每条标注责任人。</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>纪要从「回听录音两小时」变成「贴进去一分钟」，行动项再也不会漏在人名下。</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>单次省 2 小时</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>会议,纪要,行动项</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>已上线</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="Q3" s="3" t="n">
         <v>95</v>
       </c>
     </row>
@@ -923,32 +931,33 @@
           <t>根据我这周的5条工作记录，写一份周报，分「本周交付/关键数字/风险与求助/下周计划」四块，控制在400字内，别堆形容词。</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>周报从「翻聊天记录凑字数」变成「喂记录出结构」，口径统一、领导好读。</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>单次省 1.5 小时</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>周报,月报,述职</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>已上线</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="Q4" s="2" t="n">
         <v>80</v>
       </c>
     </row>
@@ -1003,32 +1012,33 @@
           <t>围绕「县域咖啡市场是否值得进入」写一份研究报告：市场规模、竞争格局、进入方式三选一、主要风险，每个结论后面标注数据来源。</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="n">
+        <v>360</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>把「搜三天资料还写不出结论」变成「两小时出带出处的初稿」。</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>单次省 6 小时</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>研究,调研,决策</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>试点</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="P5" s="3" t="n">
+      <c r="Q5" s="3" t="n">
         <v>70</v>
       </c>
     </row>
@@ -1083,32 +1093,33 @@
           <t>这是各区域季度销售额，帮我选最合适的图型，生成带同比标注的图表，配色以公司蓝为主色，重点标出下滑的两个区。</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>图表从「配色试半天」变成「说清问题就出图」，一版过会。</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>单次省 1.5 小时</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>图表,可视化,汇报</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>已上线</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="Q6" s="2" t="n">
         <v>90</v>
       </c>
     </row>
@@ -1163,32 +1174,33 @@
           <t>这是我们本月的收入、MRR、客户数与流失明细，帮我核对口径，算清MRR增速、净留存和获客成本，指出三个最该关注的异常。</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="3" t="n">
+        <v>177</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>把「三张表对不上、会上被问住」变成「一套口径、一页结论」。</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>单次省 3 小时</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>经营分析,MRR,留存</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>已上线</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P7" s="3" t="n">
+      <c r="Q7" s="3" t="n">
         <v>88</v>
       </c>
     </row>
@@ -1243,32 +1255,33 @@
           <t>帮我体检这份销售明细：缺失率、异常值、单位是否统一、有无重复订单，输出问题清单和修复建议。</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>避免「分析三天，结论因脏数据作废」这种最贵的返工。</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>单次省 2 小时</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>数据质量,清洗,校验</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>已上线</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="Q8" s="2" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1323,32 +1336,33 @@
           <t>把这份内容做成Word：A4、仿宋三号、一级标题黑体、带页码页脚，输出可编辑文件。</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K9" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>交付物直接能发，不用再手工排版半小时。</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>单次省 40 分钟</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>Word,排版,交付</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>已上线</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="P9" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>75</v>
       </c>
     </row>
@@ -1403,32 +1417,33 @@
           <t>把这份流水做成月度汇总表，用SUMIFS按部门和月份汇总，加同比增长列和柱状图。</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>表格从「拉公式拉到眼花」变成「说需求出成品」。</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>单次省 1 小时</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>Excel,公式,透视表</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>已上线</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="P10" s="2" t="n">
+      <c r="Q10" s="2" t="n">
         <v>72</v>
       </c>
     </row>
@@ -1483,32 +1498,33 @@
           <t>用公司模板做一份10页的季度复盘PPT：结论先行、每页一个观点、数据用图表讲，别写大段文字。</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>从「熬夜排版」到「半小时出可讲的稿」。</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>单次省 4 小时</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="N11" s="3" t="inlineStr">
         <is>
           <t>PPT,汇报,模板</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>已上线</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="P11" s="3" t="n">
+      <c r="Q11" s="3" t="n">
         <v>85</v>
       </c>
     </row>
@@ -1563,32 +1579,33 @@
           <t>把这个Word转成PDF，检查页码和表格有没有跨页断裂，有问题先告诉我。</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>对外交付不再「转一次修一次」。</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>单次省 20 分钟</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>PDF,转换,对外</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>已上线</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="P12" s="2" t="n">
+      <c r="Q12" s="2" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1643,32 +1660,33 @@
           <t>把这个PPT每页渲染成图片，我检查一下有没有文字溢出和错位。</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>交付前自查一分钟，省掉一轮返工和一次尴尬。</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>单次省 15 分钟</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>预览,渲染,质检</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>试点</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="P13" s="3" t="n">
+      <c r="Q13" s="3" t="n">
         <v>45</v>
       </c>
     </row>
@@ -1723,42 +1741,43 @@
           <t>重算这个工作簿的所有公式，把结果和手工核算的差异逐项列出来。</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>数字可信，汇报时不被追问第二遍。</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>单次省 30 分钟</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>公式,重算,校验</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>规划</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="P14" s="2" t="n">
+      <c r="Q14" s="2" t="n">
         <v>40</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P14"/>
+  <autoFilter ref="A1:Q14"/>
   <dataValidations count="2">
-    <dataValidation sqref="N2:N14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="只能填 已上线 / 试点 / 规划" type="list">
+    <dataValidation sqref="O2:O14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="只能填 已上线 / 试点 / 规划" type="list">
       <formula1>"已上线,试点,规划"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2319,7 +2338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2622,7 +2641,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>量化收益</t>
+          <t>单次省时(分钟)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2632,7 +2651,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>短标签，如「单次省 2 小时」，显示在卡片和详情页。</t>
+          <t>纯数字。一次任务能省多少分钟，用于算账和生成「单次省 X」标签；留空则该技能不进汇总。</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2663,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>标签</t>
+          <t>每周次数</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -2654,7 +2673,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>逗号分隔，参与搜索。</t>
+          <t>纯数字，可以是小数（0.25 = 每月一次）。写业务真实节奏，价值页用它算每周/每月节省。</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2685,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>状态</t>
+          <t>标签</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2676,7 +2695,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>已上线 / 试点 / 规划，三色标识，默认已上线。</t>
+          <t>逗号分隔，参与搜索。</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2707,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>推荐位</t>
+          <t>状态</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2698,7 +2717,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>预留字段：填「是」会在首页优先展示。</t>
+          <t>已上线 / 试点 / 规划，三色标识，默认已上线。</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2729,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>排序权重</t>
+          <t>推荐位</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -2720,29 +2739,29 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>数字越大越靠前，同分按行序。</t>
+          <t>预留字段：填「是」会在首页优先展示。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>价值案例</t>
+          <t>技能清单</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>案例编号</t>
+          <t>排序权重</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>C01、C02… 递增即可。</t>
+          <t>数字越大越靠前，同分按行序。</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2773,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>案例标题</t>
+          <t>案例编号</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2764,7 +2783,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>用「以前 X，现在 Y」的句式最有冲击力。</t>
+          <t>C01、C02… 递增即可。</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2795,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>关联技能</t>
+          <t>案例标题</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2786,7 +2805,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>填技能名称或编号。</t>
+          <t>用「以前 X，现在 Y」的句式最有冲击力。</t>
         </is>
       </c>
     </row>
@@ -2798,17 +2817,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>目标角色</t>
+          <t>关联技能</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>这个案例站在谁的视角，如「项目助理」。</t>
+          <t>填技能名称或编号。</t>
         </is>
       </c>
     </row>
@@ -2820,17 +2839,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>传统做法</t>
+          <t>目标角色</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>用 → 分隔步骤，页面会渲染成步骤清单并逐条播放；数字要真实。</t>
+          <t>这个案例站在谁的视角，如「项目助理」。</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2861,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>现在一句话</t>
+          <t>传统做法</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2852,7 +2871,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>实际用的提示词，会以打字效果呈现，并原样提供给读者复制。</t>
+          <t>用 → 分隔步骤，页面会渲染成步骤清单并逐条播放；数字要真实。</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2883,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>传统耗时(分钟)</t>
+          <t>现在一句话</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -2874,7 +2893,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>纯数字，用于计数动画和对比条。</t>
+          <t>实际用的提示词，会以打字效果呈现，并原样提供给读者复制。</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2905,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>现在耗时(分钟)</t>
+          <t>传统耗时(分钟)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2896,7 +2915,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>纯数字，通常 1-5 分钟。</t>
+          <t>纯数字，用于计数动画和对比条。</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2927,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>价值说明</t>
+          <t>现在耗时(分钟)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -2918,7 +2937,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>省下来的时间换回了什么，不要只写「效率提升」。</t>
+          <t>纯数字，通常 1-5 分钟。</t>
         </is>
       </c>
     </row>
@@ -2930,44 +2949,66 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>首页展示</t>
+          <t>价值说明</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>填「是」会出现在首页的价值预览区；建议 2-3 个。</t>
+          <t>省下来的时间换回了什么，不要只写「效率提升」。</t>
         </is>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
+          <t>价值案例</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>首页展示</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>预留字段：首页现在只放技能库，这一列暂不生效。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>使用指南</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>类型 / 标题 / 内容</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>类型填「步骤」或「常见问题」，决定它出现在指南页哪一区。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D29"/>
+  <autoFilter ref="A1:D30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>